--- a/Stats Sheet/Round Gaps/Conjure.xlsx
+++ b/Stats Sheet/Round Gaps/Conjure.xlsx
@@ -574,7 +574,7 @@
     <x:t>Kaddyn</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>nsket</x:t>
